--- a/Result/profitability/6226.xlsx
+++ b/Result/profitability/6226.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06125000000000001</v>
+        <v>-0.04125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>27.8875</v>
+        <v>28.43625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01875000000000001</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="N3" t="n">
-        <v>28.09875</v>
+        <v>29.11625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03875</v>
+        <v>0.0525</v>
       </c>
       <c r="N4" t="n">
-        <v>28.70125</v>
+        <v>29.24125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04875</v>
+        <v>0.0675</v>
       </c>
       <c r="N5" t="n">
-        <v>28.56625</v>
+        <v>28.82875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0175</v>
+        <v>0.01375</v>
       </c>
       <c r="N6" t="n">
-        <v>26.95375</v>
+        <v>27.085</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03750000000000001</v>
+        <v>-0.02250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>25.91375</v>
+        <v>26.20125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.006250000000000006</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="N8" t="n">
-        <v>26.205</v>
+        <v>26.31125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>175</v>
+      </c>
+      <c r="D75" t="n">
+        <v>121</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.06375000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.10625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8500000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02819237147595355</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.153846153846154</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0726643598615917</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
